--- a/artfynd/A 25034-2024 artfynd.xlsx
+++ b/artfynd/A 25034-2024 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>81136320</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>58110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25034-2024 artfynd.xlsx
+++ b/artfynd/A 25034-2024 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>81136320</v>
       </c>
       <c r="B5" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25034-2024 artfynd.xlsx
+++ b/artfynd/A 25034-2024 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>81136320</v>
       </c>
       <c r="B5" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25034-2024 artfynd.xlsx
+++ b/artfynd/A 25034-2024 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>81136320</v>
       </c>
       <c r="B5" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
